--- a/src/test/resources/tutorial/excluded-Header-Single-Student.xlsx
+++ b/src/test/resources/tutorial/excluded-Header-Single-Student.xlsx
@@ -108,7 +108,7 @@
         <v>4</v>
       </c>
       <c r="C2" t="n" s="9">
-        <v>20.0</v>
+        <v>21.0</v>
       </c>
     </row>
     <row r="3">
@@ -119,7 +119,7 @@
         <v>6</v>
       </c>
       <c r="C3" t="n" s="9">
-        <v>23.0</v>
+        <v>24.0</v>
       </c>
     </row>
   </sheetData>
